--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_289_R29.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_289_R29.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5327</v>
+        <v>6.2756</v>
       </c>
       <c r="E2" t="n">
-        <v>7.36</v>
+        <v>5.9013</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1727</v>
+        <v>0.3743</v>
       </c>
       <c r="G2" t="n">
         <v>1.5803</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6482</v>
+        <v>0.3912</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3239</v>
+        <v>0.8652</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6756</v>
+        <v>-0.474</v>
       </c>
       <c r="V2" t="n">
         <v>2.6805</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>N. HAYES-DAVIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2023</v>
+        <v>4.0319</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8793</v>
+        <v>5.2854</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.677</v>
+        <v>-1.2535</v>
       </c>
       <c r="G3" t="n">
-        <v>1.998</v>
+        <v>0.2624</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3492</v>
+        <v>1.8787</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3512</v>
+        <v>-1.6163</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2384</v>
+        <v>3.6896</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0068</v>
+        <v>2.0404</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2317</v>
+        <v>1.6492</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2404</v>
+        <v>-3.4272</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3424</v>
+        <v>-0.1617</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.5829</v>
+        <v>-3.2655</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1668</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8566</v>
+        <v>-1.0846</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3101</v>
+        <v>0.3181</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2836</v>
+        <v>2.6805</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4975</v>
+        <v>2.6805</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. HAYES-DAVIS</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1748</v>
+        <v>3.7146</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4283</v>
+        <v>5.1899</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2535</v>
+        <v>-1.4754</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2624</v>
+        <v>1.998</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8787</v>
+        <v>2.3492</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6163</v>
+        <v>-0.3512</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6896</v>
+        <v>4.2384</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0404</v>
+        <v>2.0068</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6492</v>
+        <v>2.2317</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.4272</v>
+        <v>-2.2404</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1617</v>
+        <v>0.3424</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.2655</v>
+        <v>-2.5829</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6237</v>
+        <v>-0.6546</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.9417</v>
+        <v>-0.5461</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3181</v>
+        <v>-0.1085</v>
       </c>
       <c r="V4" t="n">
-        <v>2.6805</v>
+        <v>0.2836</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6805</v>
+        <v>1.4975</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6324</v>
+        <v>1.402</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4794</v>
+        <v>0.9211</v>
       </c>
       <c r="F5" t="n">
-        <v>1.153</v>
+        <v>0.4809</v>
       </c>
       <c r="G5" t="n">
         <v>1.2516</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9892</v>
+        <v>0.7587</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6765</v>
+        <v>0.1182</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3126</v>
+        <v>0.6405</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8859</v>
+        <v>-0.9867</v>
       </c>
       <c r="E6" t="n">
         <v>0.5780999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4641</v>
+        <v>-1.5649</v>
       </c>
       <c r="G6" t="n">
         <v>-3.5815</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.771</v>
+        <v>-0.8718</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1098</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6611</v>
+        <v>-0.762</v>
       </c>
       <c r="V6" t="n">
         <v>2.5387</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9808</v>
+        <v>-2.7956</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0125</v>
+        <v>0.1305</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9933</v>
+        <v>-2.9261</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1879</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1125</v>
+        <v>0.0727</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0378</v>
+        <v>0.0294</v>
       </c>
       <c r="V7" t="n">
         <v>-2.6805</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. HOLMES</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3998</v>
+        <v>-2.8942</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4276</v>
+        <v>-2.2896</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.8273</v>
+        <v>-0.6045</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.3364</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.904</v>
+        <v>-0.6915</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.4324</v>
+        <v>-0.1002</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5348000000000001</v>
+        <v>0.4985</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1472</v>
+        <v>0.5889</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8016</v>
+        <v>-1.2903</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.222</v>
+        <v>-0.6012</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.5796</v>
+        <v>-0.6891</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6959</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2232</v>
+        <v>-1.319</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1098</v>
+        <v>-0.3811</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1133</v>
+        <v>-0.9379</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W8" t="n">
         <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>R. HOLMES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9694</v>
+        <v>-3.4773</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0288</v>
+        <v>0.1484</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9406</v>
+        <v>-3.6257</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-3.3364</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6915</v>
+        <v>-0.904</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1002</v>
+        <v>-2.4324</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4985</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5889</v>
+        <v>0.1472</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2903</v>
+        <v>-2.8016</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6012</v>
+        <v>-0.222</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6891</v>
+        <v>-2.5796</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.3942</v>
+        <v>-0.3007</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1202</v>
+        <v>-0.389</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.274</v>
+        <v>0.0883</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
         <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.081</v>
+        <v>-4.2755</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.0855</v>
+        <v>-1.8519</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0045</v>
+        <v>-2.4236</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.624</v>
+        <v>-3.8922</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0983</v>
+        <v>0.6015</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5257</v>
+        <v>-4.4937</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9341</v>
+        <v>-1.3086</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.7093</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5727</v>
+        <v>-2.0179</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6899</v>
+        <v>-2.5837</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7369</v>
+        <v>-0.1078</v>
       </c>
       <c r="O10" t="n">
-        <v>0.047</v>
+        <v>-2.4759</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5515</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3694</v>
+        <v>-0.6152</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6721</v>
+        <v>-0.4558</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3027</v>
+        <v>-0.1595</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.276</v>
+        <v>-5.2985</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5163</v>
+        <v>-4.7316</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7597</v>
+        <v>-0.5668</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8922</v>
+        <v>-1.624</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6015</v>
+        <v>-0.0983</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.4937</v>
+        <v>-1.5257</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3086</v>
+        <v>-0.9341</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7093</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0179</v>
+        <v>-1.5727</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5837</v>
+        <v>-0.6899</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1078</v>
+        <v>-0.7369</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.4759</v>
+        <v>0.047</v>
       </c>
       <c r="P11" t="n">
-        <v>0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6157</v>
+        <v>-0.5869</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1202</v>
+        <v>-0.3183</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4955</v>
+        <v>-0.2686</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.050699999999998</v>
+        <v>-4.303699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>8.534599999999998</v>
+        <v>9.281599999999997</v>
       </c>
       <c r="F12" t="n">
         <v>-13.5853</v>
@@ -1363,13 +1363,13 @@
         <v>-16.5622</v>
       </c>
       <c r="J12" t="n">
-        <v>8.9924</v>
+        <v>8.992399999999998</v>
       </c>
       <c r="K12" t="n">
         <v>9.2111</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2186000000000006</v>
+        <v>-0.2185999999999997</v>
       </c>
       <c r="M12" t="n">
         <v>-17.3141</v>
@@ -1390,13 +1390,13 @@
         <v>12.7575</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.6391</v>
+        <v>-3.8922</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.0047</v>
+        <v>-2.258</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.634</v>
+        <v>-1.6342</v>
       </c>
       <c r="V12" t="n">
         <v>4.4306</v>
@@ -1405,13 +1405,13 @@
         <v>11.8252</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.3947</v>
+        <v>-7.394700000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.221</v>
+        <v>5.4908</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5819</v>
+        <v>5.5592</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3609</v>
+        <v>-0.0684</v>
       </c>
       <c r="G13" t="n">
-        <v>4.3918</v>
+        <v>3.0348</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4839</v>
+        <v>-2.1044</v>
       </c>
       <c r="I13" t="n">
-        <v>3.908</v>
+        <v>5.1393</v>
       </c>
       <c r="J13" t="n">
-        <v>5.1532</v>
+        <v>4.5754</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8739</v>
+        <v>-1.1995</v>
       </c>
       <c r="L13" t="n">
-        <v>4.2793</v>
+        <v>5.7749</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7613</v>
+        <v>-1.5405</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.39</v>
+        <v>-0.9049</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3713</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R13" t="n">
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3473</v>
+        <v>0.863</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4288</v>
+        <v>0.0868</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9186</v>
+        <v>0.7762</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.214</v>
+        <v>3.2166</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1382</v>
+        <v>5.1367</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6772</v>
+        <v>5.464</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5389</v>
+        <v>-0.3273</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0348</v>
+        <v>4.3918</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.1044</v>
+        <v>0.4839</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1393</v>
+        <v>3.908</v>
       </c>
       <c r="J14" t="n">
-        <v>4.5754</v>
+        <v>5.1532</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.1995</v>
+        <v>0.8739</v>
       </c>
       <c r="L14" t="n">
-        <v>5.7749</v>
+        <v>4.2793</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5405</v>
+        <v>-0.7613</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9049</v>
+        <v>-0.39</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.3713</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5105</v>
+        <v>1.263</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2047</v>
+        <v>0.3108</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3058</v>
+        <v>0.9522</v>
       </c>
       <c r="V14" t="n">
-        <v>3.2166</v>
+        <v>-1.214</v>
       </c>
       <c r="W14" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4262</v>
+        <v>2.9994</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3946</v>
+        <v>3.1024</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0315</v>
+        <v>-0.1029</v>
       </c>
       <c r="G15" t="n">
         <v>3.1607</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5026</v>
+        <v>0.0707</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5895</v>
+        <v>0.1182</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.0474</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9751</v>
+        <v>2.918</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6439</v>
+        <v>2.3516</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3312</v>
+        <v>0.5664</v>
       </c>
       <c r="G16" t="n">
         <v>0.1506</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3921</v>
+        <v>-0.4492</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6642</v>
+        <v>0.0435</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7279</v>
+        <v>-0.4927</v>
       </c>
       <c r="V16" t="n">
         <v>3.2166</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RHODEN</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.049</v>
+        <v>-0.1948</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2975</v>
+        <v>0.2521</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3465</v>
+        <v>-0.4469</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.032</v>
+        <v>-0.9134</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0888</v>
+        <v>-2.2953</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0568</v>
+        <v>1.3819</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6442</v>
+        <v>0.0159</v>
       </c>
       <c r="K17" t="n">
-        <v>1.163</v>
+        <v>-1.7373</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5188</v>
+        <v>1.7532</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6762</v>
+        <v>-0.9294</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2518</v>
+        <v>-0.5581</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5756</v>
+        <v>-0.3713</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8386</v>
+        <v>1.095</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9006</v>
+        <v>0.2361</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0619</v>
+        <v>0.8588</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>J. RHODEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0926</v>
+        <v>-0.6723</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4868</v>
+        <v>-0.2923</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5793</v>
+        <v>-0.3801</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3247</v>
+        <v>-0.032</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2305</v>
+        <v>-0.0888</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0942</v>
+        <v>0.0568</v>
       </c>
       <c r="J18" t="n">
-        <v>1.908</v>
+        <v>0.6442</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6504</v>
+        <v>1.163</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2576</v>
+        <v>-0.5188</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5833</v>
+        <v>-0.6762</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4199</v>
+        <v>-1.2518</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8366</v>
+        <v>0.5756</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9796</v>
+        <v>0.2153</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5272</v>
+        <v>0.3108</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4525</v>
+        <v>-0.0955</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.3969</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2785</v>
+        <v>-0.8287</v>
       </c>
       <c r="E19" t="n">
-        <v>0.37</v>
+        <v>0.3139</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6485</v>
+        <v>-1.1426</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9134</v>
+        <v>0.716</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2953</v>
+        <v>0.1706</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3819</v>
+        <v>0.5454</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0159</v>
+        <v>0.1408</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.7373</v>
+        <v>0.0672</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7532</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9294</v>
+        <v>0.5752</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5581</v>
+        <v>0.1034</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3713</v>
+        <v>0.4718</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0113</v>
+        <v>-0.0266</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3541</v>
+        <v>0.1731</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6572</v>
+        <v>-0.1997</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>-1.7501</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3905</v>
+        <v>-0.9689</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7857</v>
+        <v>-1.3681</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1762</v>
+        <v>0.3992</v>
       </c>
       <c r="G20" t="n">
-        <v>0.716</v>
+        <v>-2.1926</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1706</v>
+        <v>-1.5702</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5454</v>
+        <v>-0.6224</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1408</v>
+        <v>-1.8636</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0672</v>
+        <v>-1.5055</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>-0.3581</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5752</v>
+        <v>-0.329</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1034</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4718</v>
+        <v>-0.2643</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4116</v>
+        <v>0.2959</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6449</v>
+        <v>0.4955</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2333</v>
+        <v>-0.1997</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0025</v>
+        <v>-1.1528</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3681</v>
+        <v>-0.103</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3656</v>
+        <v>-1.0498</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1926</v>
+        <v>1.3247</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5702</v>
+        <v>0.2305</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6224</v>
+        <v>1.0942</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.8636</v>
+        <v>1.908</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5055</v>
+        <v>1.6504</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3581</v>
+        <v>0.2576</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.329</v>
+        <v>-0.5833</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-1.4199</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2643</v>
+        <v>0.8366</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2623</v>
+        <v>-0.0806</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4955</v>
+        <v>-0.0626</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2333</v>
+        <v>-0.018</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.3969</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6552</v>
+        <v>-1.6723</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8851</v>
+        <v>0.7671</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5402</v>
+        <v>-2.4394</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8825</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6216</v>
+        <v>0.6045</v>
       </c>
       <c r="T22" t="n">
-        <v>0.13</v>
+        <v>0.0121</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4916</v>
+        <v>0.5924</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9304</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9226</v>
+        <v>-2.5187</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4779</v>
+        <v>-1.242</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4447</v>
+        <v>-1.2766</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1144</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8984</v>
+        <v>-0.4944</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4402</v>
+        <v>-0.2043</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4582</v>
+        <v>-0.2902</v>
       </c>
       <c r="V23" t="n">
         <v>-1.214</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3191</v>
+        <v>-3.4858</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1552</v>
+        <v>-0.6834</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1639</v>
+        <v>-2.8024</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3224</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>1.4493</v>
+        <v>1.2825</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3576</v>
+        <v>0.1142</v>
       </c>
       <c r="U24" t="n">
-        <v>1.8069</v>
+        <v>1.1683</v>
       </c>
       <c r="V24" t="n">
         <v>-2.8223</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.050499999999998</v>
+        <v>5.050600000000005</v>
       </c>
       <c r="E25" t="n">
         <v>14.1215</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.070799999999998</v>
+        <v>-9.0708</v>
       </c>
       <c r="G25" t="n">
         <v>8.321299999999999</v>
@@ -2380,7 +2380,7 @@
         <v>17.3138</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9701999999999995</v>
+        <v>0.9701999999999997</v>
       </c>
       <c r="L25" t="n">
         <v>16.3436</v>
@@ -2404,16 +2404,16 @@
         <v>9.278400000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>4.638999999999999</v>
+        <v>4.6391</v>
       </c>
       <c r="T25" t="n">
-        <v>1.6343</v>
+        <v>1.6342</v>
       </c>
       <c r="U25" t="n">
-        <v>3.005</v>
+        <v>3.0047</v>
       </c>
       <c r="V25" t="n">
-        <v>-4.4306</v>
+        <v>-4.430599999999999</v>
       </c>
       <c r="W25" t="n">
         <v>7.9308</v>
